--- a/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,43; 67,42</t>
+          <t>55,18; 68,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,04; 63,21</t>
+          <t>49,61; 63,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 68,29</t>
+          <t>48,59; 68,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,14; 62,01</t>
+          <t>47,92; 60,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,55; 62,27</t>
+          <t>47,85; 61,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,61; 69,78</t>
+          <t>50,42; 68,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,32; 63,0</t>
+          <t>53,24; 62,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,37; 60,84</t>
+          <t>50,49; 60,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,34; 66,69</t>
+          <t>52,55; 65,81</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,35; 71,55</t>
+          <t>61,94; 71,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,95; 53,72</t>
+          <t>42,62; 53,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,72; 67,06</t>
+          <t>54,34; 66,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,8; 70,76</t>
+          <t>60,71; 70,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,49; 58,47</t>
+          <t>48,48; 58,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,39; 71,73</t>
+          <t>59,88; 71,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,79; 69,68</t>
+          <t>62,59; 69,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,43; 54,79</t>
+          <t>47,45; 55,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,0; 67,71</t>
+          <t>58,94; 67,82</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,28; 69,78</t>
+          <t>57,47; 69,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,83; 58,53</t>
+          <t>46,86; 58,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,13; 71,78</t>
+          <t>60,15; 72,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,23; 65,26</t>
+          <t>51,94; 65,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,56; 56,56</t>
+          <t>44,38; 56,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,87; 59,44</t>
+          <t>45,85; 59,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,37; 65,67</t>
+          <t>56,24; 65,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,89; 56,11</t>
+          <t>47,52; 56,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,34; 63,44</t>
+          <t>54,22; 63,44</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,72; 69,91</t>
+          <t>57,73; 70,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,86; 56,37</t>
+          <t>44,27; 57,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,07; 74,06</t>
+          <t>54,63; 73,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,83; 69,88</t>
+          <t>58,64; 70,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,44; 58,92</t>
+          <t>45,1; 58,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,41; 64,27</t>
+          <t>49,76; 64,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,69; 68,7</t>
+          <t>60,0; 68,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,9; 56,76</t>
+          <t>46,87; 56,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,54; 66,67</t>
+          <t>54,07; 65,95</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,57; 67,45</t>
+          <t>61,42; 67,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,7; 54,71</t>
+          <t>48,77; 54,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,8; 68,11</t>
+          <t>58,66; 67,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,78</t>
+          <t>58,79; 64,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,52</t>
+          <t>49,67; 55,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,48; 62,35</t>
+          <t>54,44; 62,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,96; 65,19</t>
+          <t>60,97; 65,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,15; 54,4</t>
+          <t>50,06; 54,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,37; 63,2</t>
+          <t>57,54; 63,67</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>88852</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33798</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79228</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68330</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37057</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>168079</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>143091</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>70855</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>79704; 98991</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>65312; 83928</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27942; 39119</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>69664; 88244</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>59417; 76796</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30983; 42370</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>154292; 181961</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>129166; 154052</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>62514; 78290</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>157805</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100596</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96801</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>176810</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>136635</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>120031</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>334615</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>237231</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>216833</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>146330; 169890</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>88841; 111730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>86565; 106684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162902; 189288</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>124153; 148690</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>108895; 130543</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>315817; 351678</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>220407; 255763</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>201065; 231360</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>99278</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99780</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115565</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>93195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94293</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>111383</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>192472</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>194073</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>226947</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>89806; 109155</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87840; 110522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>104593; 126740</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82360; 103793</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>82715; 105674</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>96994; 126005</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>177051; 206277</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>177660; 210805</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>208980; 244536</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>110014</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87202</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169743</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116071</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91243</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>177218</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>226084</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>178445</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>346961</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>98912; 120461</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>76419; 98890</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>149928; 201912</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105527; 126060</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>78200; 101396</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>152003; 197304</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>210782; 241637</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>162171; 194354</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>313564; 382472</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>455948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>362339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>415906</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>445689</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>921251</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>752840</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>861595</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>435016; 476483</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>341465; 382945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>390190; 449372</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>442269; 486898</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>367598; 413510</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>413919; 476641</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>890540; 951405</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>720906; 781491</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>820184; 907555</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,18; 68,53</t>
+          <t>55,1; 67,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,61; 63,75</t>
+          <t>49,99; 63,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,59; 68,02</t>
+          <t>47,91; 67,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,92; 60,71</t>
+          <t>47,55; 61,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,85; 61,85</t>
+          <t>47,63; 62,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,42; 68,96</t>
+          <t>50,36; 68,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,24; 62,79</t>
+          <t>53,36; 62,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,49; 60,22</t>
+          <t>50,67; 60,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,55; 65,81</t>
+          <t>53,09; 66,77</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,94; 71,91</t>
+          <t>61,79; 71,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,62; 53,6</t>
+          <t>42,24; 53,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,34; 66,97</t>
+          <t>54,02; 67,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,71; 70,54</t>
+          <t>61,09; 71,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,48; 58,06</t>
+          <t>47,94; 58,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,88; 71,79</t>
+          <t>60,11; 72,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,59; 69,7</t>
+          <t>62,71; 69,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,45; 55,06</t>
+          <t>47,19; 54,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,94; 67,82</t>
+          <t>59,16; 68,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,47; 69,86</t>
+          <t>57,65; 70,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,86; 58,96</t>
+          <t>47,33; 59,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,15; 72,89</t>
+          <t>59,89; 72,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,94; 65,46</t>
+          <t>52,09; 65,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,38; 56,7</t>
+          <t>44,71; 56,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,85; 59,56</t>
+          <t>45,49; 59,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,24; 65,52</t>
+          <t>56,36; 65,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,52; 56,39</t>
+          <t>48,02; 56,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,22; 63,44</t>
+          <t>53,73; 63,74</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,73; 70,31</t>
+          <t>58,56; 70,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,27; 57,28</t>
+          <t>44,3; 56,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,63; 73,57</t>
+          <t>54,91; 73,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,64; 70,05</t>
+          <t>58,61; 70,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,1; 58,48</t>
+          <t>46,48; 59,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,76; 64,59</t>
+          <t>49,65; 64,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,0; 68,79</t>
+          <t>60,0; 68,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,87; 56,17</t>
+          <t>46,9; 56,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,07; 65,95</t>
+          <t>54,86; 67,14</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,27</t>
+          <t>61,24; 67,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,77; 54,69</t>
+          <t>48,64; 54,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,66; 67,56</t>
+          <t>58,92; 68,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58,79; 64,73</t>
+          <t>59,04; 64,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,67; 55,88</t>
+          <t>49,55; 55,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,44; 62,69</t>
+          <t>54,1; 62,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,14</t>
+          <t>60,97; 65,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,06; 54,26</t>
+          <t>50,14; 54,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,67</t>
+          <t>57,7; 63,37</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79704; 98991</t>
+          <t>79591; 98113</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65312; 83928</t>
+          <t>65813; 83541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27942; 39119</t>
+          <t>27555; 39023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69664; 88244</t>
+          <t>69120; 89704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59417; 76796</t>
+          <t>59141; 77112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30983; 42370</t>
+          <t>30940; 42351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>154292; 181961</t>
+          <t>154641; 181693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>129166; 154052</t>
+          <t>129635; 155284</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62514; 78290</t>
+          <t>63154; 79425</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146330; 169890</t>
+          <t>145989; 169648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88841; 111730</t>
+          <t>88051; 112164</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86565; 106684</t>
+          <t>86057; 107172</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162902; 189288</t>
+          <t>163915; 191024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>124153; 148690</t>
+          <t>122775; 148933</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>108895; 130543</t>
+          <t>109306; 131387</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>315817; 351678</t>
+          <t>316411; 352092</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>220407; 255763</t>
+          <t>219207; 254661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201065; 231360</t>
+          <t>201832; 232299</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89806; 109155</t>
+          <t>90085; 110108</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87840; 110522</t>
+          <t>88716; 111403</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104593; 126740</t>
+          <t>104136; 125461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82360; 103793</t>
+          <t>82604; 103156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82715; 105674</t>
+          <t>83325; 105210</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96994; 126005</t>
+          <t>96240; 125285</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>177051; 206277</t>
+          <t>177438; 205899</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>177660; 210805</t>
+          <t>179502; 209569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>208980; 244536</t>
+          <t>207092; 245684</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98912; 120461</t>
+          <t>100342; 121531</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76419; 98890</t>
+          <t>76470; 98232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149928; 201912</t>
+          <t>150693; 201725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105527; 126060</t>
+          <t>105471; 126590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78200; 101396</t>
+          <t>80577; 102749</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>152003; 197304</t>
+          <t>151679; 195979</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>210782; 241637</t>
+          <t>210780; 240168</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162171; 194354</t>
+          <t>162271; 193877</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>313564; 382472</t>
+          <t>318152; 389379</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>435016; 476483</t>
+          <t>433746; 477138</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>341465; 382945</t>
+          <t>340584; 383439</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>390190; 449372</t>
+          <t>391941; 454634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>442269; 486898</t>
+          <t>444078; 487362</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>367598; 413510</t>
+          <t>366690; 411755</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>413919; 476641</t>
+          <t>411370; 473302</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>890540; 951405</t>
+          <t>890450; 953410</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>720906; 781491</t>
+          <t>722137; 784270</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>820184; 907555</t>
+          <t>822563; 903394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55,03%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>61,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>56,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,03%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,1; 67,92</t>
+          <t>48,14; 62,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,99; 63,45</t>
+          <t>47,55; 62,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,91; 67,85</t>
+          <t>52,4; 71,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,55; 61,71</t>
+          <t>54,43; 67,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,63; 62,1</t>
+          <t>50,04; 63,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,36; 68,93</t>
+          <t>48,02; 68,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,36; 62,69</t>
+          <t>53,32; 63,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,67; 60,7</t>
+          <t>51,37; 60,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,09; 66,77</t>
+          <t>52,87; 67,19</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>66,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>48,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60,77%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>53,36%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,79; 71,81</t>
+          <t>60,8; 70,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,24; 53,81</t>
+          <t>48,49; 58,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,02; 67,28</t>
+          <t>59,87; 72,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,09; 71,19</t>
+          <t>61,35; 71,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,94; 58,16</t>
+          <t>42,95; 53,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,11; 72,25</t>
+          <t>54,94; 67,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,71; 69,78</t>
+          <t>62,79; 69,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,19; 54,82</t>
+          <t>47,43; 54,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,16; 68,09</t>
+          <t>59,87; 68,19</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54,66%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>63,54%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>53,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,65; 70,47</t>
+          <t>52,23; 65,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,33; 59,43</t>
+          <t>44,56; 56,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,89; 72,15</t>
+          <t>48,07; 61,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,09; 65,05</t>
+          <t>57,28; 69,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,71; 56,45</t>
+          <t>46,83; 58,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,49; 59,22</t>
+          <t>58,78; 71,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,36; 65,4</t>
+          <t>56,37; 65,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,02; 56,06</t>
+          <t>47,89; 56,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,73; 63,74</t>
+          <t>55,66; 64,41</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52,63%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>64,21%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>50,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61,85%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,63%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,56; 70,93</t>
+          <t>58,83; 69,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,3; 56,9</t>
+          <t>46,44; 58,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,91; 73,5</t>
+          <t>52,12; 65,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,61; 70,35</t>
+          <t>57,72; 69,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 59,26</t>
+          <t>43,86; 56,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,65; 64,15</t>
+          <t>55,4; 66,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,0; 68,37</t>
+          <t>60,69; 68,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,9; 56,03</t>
+          <t>46,9; 56,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,86; 67,14</t>
+          <t>55,94; 65,1</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,24; 67,36</t>
+          <t>59,04; 64,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,64; 54,76</t>
+          <t>49,71; 55,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,92; 68,35</t>
+          <t>56,28; 63,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,79</t>
+          <t>61,57; 67,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,55; 55,64</t>
+          <t>48,7; 54,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,1; 62,25</t>
+          <t>59,24; 65,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,28</t>
+          <t>60,96; 65,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,14; 54,46</t>
+          <t>50,15; 54,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,7; 63,37</t>
+          <t>58,67; 63,5</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79228</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68330</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31202</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>88852</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>74761</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33798</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79228</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68330</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70855</t>
+          <t>61534</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79591; 98113</t>
+          <t>69981; 90136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65813; 83541</t>
+          <t>59039; 77315</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27555; 39023</t>
+          <t>26481; 35948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69120; 89704</t>
+          <t>78625; 97395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59141; 77112</t>
+          <t>65884; 83220</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30940; 42351</t>
+          <t>25013; 35439</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>154641; 181693</t>
+          <t>154536; 182588</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>129635; 155284</t>
+          <t>131417; 155629</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63154; 79425</t>
+          <t>54261; 68950</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>176810</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136635</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104036</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>157805</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>100596</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>96801</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>176810</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>136635</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>120031</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>216833</t>
+          <t>193849</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>145989; 169648</t>
+          <t>163160; 189869</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88051; 112164</t>
+          <t>124182; 149740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86057; 107172</t>
+          <t>93946; 113351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163915; 191024</t>
+          <t>144950; 169044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122775; 148933</t>
+          <t>89521; 111982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>109306; 131387</t>
+          <t>79949; 98592</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>316411; 352092</t>
+          <t>316808; 351620</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>219207; 254661</t>
+          <t>220318; 254510</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201832; 232299</t>
+          <t>181047; 206230</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>93195</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94293</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108861</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>99278</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>99780</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115565</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93195</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94293</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>116071</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>226947</t>
+          <t>224931</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90085; 110108</t>
+          <t>82816; 103491</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88716; 111403</t>
+          <t>83053; 105421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104136; 125461</t>
+          <t>95743; 121950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82604; 103156</t>
+          <t>89500; 109039</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83325; 105210</t>
+          <t>87775; 109705</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96240; 125285</t>
+          <t>103161; 125761</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>177438; 205899</t>
+          <t>177475; 206753</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>179502; 209569</t>
+          <t>179025; 209769</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>207092; 245684</t>
+          <t>208536; 241346</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>206</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116071</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91243</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176046</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>110014</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>87202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>169743</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116071</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91243</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>177218</t>
+          <t>156006</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>346961</t>
+          <t>332052</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100342; 121531</t>
+          <t>105874; 125746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76470; 98232</t>
+          <t>80517; 102150</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150693; 201725</t>
+          <t>152518; 192807</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105471; 126590</t>
+          <t>98893; 119779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80577; 102749</t>
+          <t>75726; 97315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151679; 195979</t>
+          <t>141538; 170265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>210780; 240168</t>
+          <t>213204; 241353</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162271; 193877</t>
+          <t>162296; 196399</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>318152; 389379</t>
+          <t>306596; 356800</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>538</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>465303</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>433746; 477138</t>
+          <t>444098; 487265</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>340584; 383439</t>
+          <t>367827; 410849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>391941; 454634</t>
+          <t>393508; 445390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>444078; 487362</t>
+          <t>436076; 477724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>366690; 411755</t>
+          <t>340992; 383063</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>411370; 473302</t>
+          <t>372390; 411409</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>890450; 953410</t>
+          <t>890344; 952094</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>722137; 784270</t>
+          <t>722197; 783510</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>822563; 903394</t>
+          <t>779070; 843161</t>
         </is>
       </c>
     </row>
